--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497156</v>
+        <v>121497159</v>
       </c>
       <c r="B3" t="n">
-        <v>97055</v>
+        <v>56563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598473</v>
+        <v>598447</v>
       </c>
       <c r="R3" t="n">
-        <v>7178492</v>
+        <v>7178538</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497159</v>
+        <v>121497156</v>
       </c>
       <c r="B5" t="n">
-        <v>56563</v>
+        <v>97055</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598447</v>
+        <v>598473</v>
       </c>
       <c r="R5" t="n">
-        <v>7178538</v>
+        <v>7178492</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497157</v>
+        <v>121497159</v>
       </c>
       <c r="B2" t="n">
-        <v>97049</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598471</v>
+        <v>598447</v>
       </c>
       <c r="R2" t="n">
-        <v>7178490</v>
+        <v>7178538</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497159</v>
+        <v>121497160</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598447</v>
+        <v>598732</v>
       </c>
       <c r="R3" t="n">
-        <v>7178538</v>
+        <v>7178834</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497160</v>
+        <v>121497157</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>97052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598732</v>
+        <v>598471</v>
       </c>
       <c r="R4" t="n">
-        <v>7178834</v>
+        <v>7178490</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1023,7 @@
         <v>121497156</v>
       </c>
       <c r="B5" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497159</v>
+        <v>121497156</v>
       </c>
       <c r="B2" t="n">
-        <v>56566</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598447</v>
+        <v>598473</v>
       </c>
       <c r="R2" t="n">
-        <v>7178538</v>
+        <v>7178492</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497160</v>
+        <v>121497157</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>97052</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598732</v>
+        <v>598471</v>
       </c>
       <c r="R3" t="n">
-        <v>7178834</v>
+        <v>7178490</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497157</v>
+        <v>121497160</v>
       </c>
       <c r="B4" t="n">
-        <v>97052</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598471</v>
+        <v>598732</v>
       </c>
       <c r="R4" t="n">
-        <v>7178490</v>
+        <v>7178834</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497156</v>
+        <v>121497159</v>
       </c>
       <c r="B5" t="n">
-        <v>97058</v>
+        <v>56566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598473</v>
+        <v>598447</v>
       </c>
       <c r="R5" t="n">
-        <v>7178492</v>
+        <v>7178538</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497156</v>
+        <v>121497160</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598473</v>
+        <v>598732</v>
       </c>
       <c r="R2" t="n">
-        <v>7178492</v>
+        <v>7178834</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497157</v>
+        <v>121497159</v>
       </c>
       <c r="B3" t="n">
-        <v>97052</v>
+        <v>56567</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598471</v>
+        <v>598447</v>
       </c>
       <c r="R3" t="n">
-        <v>7178490</v>
+        <v>7178538</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497160</v>
+        <v>121497156</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>97064</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598732</v>
+        <v>598473</v>
       </c>
       <c r="R4" t="n">
-        <v>7178834</v>
+        <v>7178492</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497159</v>
+        <v>121497157</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>97058</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598447</v>
+        <v>598471</v>
       </c>
       <c r="R5" t="n">
-        <v>7178538</v>
+        <v>7178490</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121497160</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497159</v>
+        <v>121497156</v>
       </c>
       <c r="B3" t="n">
-        <v>56567</v>
+        <v>97065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598447</v>
+        <v>598473</v>
       </c>
       <c r="R3" t="n">
-        <v>7178538</v>
+        <v>7178492</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497156</v>
+        <v>121497157</v>
       </c>
       <c r="B4" t="n">
-        <v>97064</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598473</v>
+        <v>598471</v>
       </c>
       <c r="R4" t="n">
-        <v>7178492</v>
+        <v>7178490</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497157</v>
+        <v>121497159</v>
       </c>
       <c r="B5" t="n">
-        <v>97058</v>
+        <v>56568</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,34 +1027,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598471</v>
+        <v>598447</v>
       </c>
       <c r="R5" t="n">
-        <v>7178490</v>
+        <v>7178538</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497160</v>
+        <v>121497159</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598732</v>
+        <v>598447</v>
       </c>
       <c r="R2" t="n">
-        <v>7178834</v>
+        <v>7178538</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497157</v>
+        <v>121497160</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598471</v>
+        <v>598732</v>
       </c>
       <c r="R4" t="n">
-        <v>7178490</v>
+        <v>7178834</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497159</v>
+        <v>121497157</v>
       </c>
       <c r="B5" t="n">
-        <v>56568</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598447</v>
+        <v>598471</v>
       </c>
       <c r="R5" t="n">
-        <v>7178538</v>
+        <v>7178490</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497159</v>
+        <v>121497156</v>
       </c>
       <c r="B2" t="n">
-        <v>56568</v>
+        <v>97065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598447</v>
+        <v>598473</v>
       </c>
       <c r="R2" t="n">
-        <v>7178538</v>
+        <v>7178492</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497156</v>
+        <v>121497157</v>
       </c>
       <c r="B3" t="n">
-        <v>97065</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598473</v>
+        <v>598471</v>
       </c>
       <c r="R3" t="n">
-        <v>7178492</v>
+        <v>7178490</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497160</v>
+        <v>121497159</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>56568</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598732</v>
+        <v>598447</v>
       </c>
       <c r="R4" t="n">
-        <v>7178834</v>
+        <v>7178538</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497157</v>
+        <v>121497160</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598471</v>
+        <v>598732</v>
       </c>
       <c r="R5" t="n">
-        <v>7178490</v>
+        <v>7178834</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497159</v>
+        <v>121497157</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598447</v>
+        <v>598471</v>
       </c>
       <c r="R2" t="n">
-        <v>7178538</v>
+        <v>7178490</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497157</v>
+        <v>121497159</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598471</v>
+        <v>598447</v>
       </c>
       <c r="R3" t="n">
-        <v>7178490</v>
+        <v>7178538</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497160</v>
+        <v>121497156</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>97073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598732</v>
+        <v>598473</v>
       </c>
       <c r="R4" t="n">
-        <v>7178834</v>
+        <v>7178492</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497156</v>
+        <v>121497160</v>
       </c>
       <c r="B5" t="n">
-        <v>97073</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598473</v>
+        <v>598732</v>
       </c>
       <c r="R5" t="n">
-        <v>7178492</v>
+        <v>7178834</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497159</v>
+        <v>121497156</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>97073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598447</v>
+        <v>598473</v>
       </c>
       <c r="R3" t="n">
-        <v>7178538</v>
+        <v>7178492</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497156</v>
+        <v>121497160</v>
       </c>
       <c r="B4" t="n">
-        <v>97073</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598473</v>
+        <v>598732</v>
       </c>
       <c r="R4" t="n">
-        <v>7178492</v>
+        <v>7178834</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497160</v>
+        <v>121497159</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598732</v>
+        <v>598447</v>
       </c>
       <c r="R5" t="n">
-        <v>7178834</v>
+        <v>7178538</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497157</v>
+        <v>121497160</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598471</v>
+        <v>598732</v>
       </c>
       <c r="R2" t="n">
-        <v>7178490</v>
+        <v>7178834</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121497156</v>
+        <v>121497159</v>
       </c>
       <c r="B3" t="n">
-        <v>97073</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598473</v>
+        <v>598447</v>
       </c>
       <c r="R3" t="n">
-        <v>7178492</v>
+        <v>7178538</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497160</v>
+        <v>121497156</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>97073</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598732</v>
+        <v>598473</v>
       </c>
       <c r="R4" t="n">
-        <v>7178834</v>
+        <v>7178492</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497159</v>
+        <v>121497157</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,43 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598447</v>
+        <v>598471</v>
       </c>
       <c r="R5" t="n">
-        <v>7178538</v>
+        <v>7178490</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1130,6 +1130,253 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122536600</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56589</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjärnmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598566</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7178644</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122536599</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56589</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjärnmyran, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598450</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7178455</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>122536600</v>
       </c>
       <c r="B6" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,6 +1149,11 @@
       </c>
       <c r="E6" t="n">
         <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1261,7 +1266,7 @@
         <v>122536599</v>
       </c>
       <c r="B7" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,6 +1280,11 @@
       </c>
       <c r="E7" t="n">
         <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536600</v>
+        <v>122536599</v>
       </c>
       <c r="B6" t="n">
         <v>56593</v>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598566</v>
+        <v>598450</v>
       </c>
       <c r="R6" t="n">
-        <v>7178644</v>
+        <v>7178455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536599</v>
+        <v>122536600</v>
       </c>
       <c r="B7" t="n">
         <v>56593</v>
@@ -1298,12 +1293,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598450</v>
+        <v>598566</v>
       </c>
       <c r="R7" t="n">
-        <v>7178455</v>
+        <v>7178644</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536599</v>
+        <v>122536600</v>
       </c>
       <c r="B6" t="n">
         <v>56593</v>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598450</v>
+        <v>598566</v>
       </c>
       <c r="R6" t="n">
-        <v>7178455</v>
+        <v>7178644</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1263,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536600</v>
+        <v>122536599</v>
       </c>
       <c r="B7" t="n">
         <v>56593</v>
@@ -1293,12 +1298,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598566</v>
+        <v>598450</v>
       </c>
       <c r="R7" t="n">
-        <v>7178644</v>
+        <v>7178455</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,12 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536600</v>
+        <v>122536599</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598566</v>
+        <v>598450</v>
       </c>
       <c r="R6" t="n">
-        <v>7178644</v>
+        <v>7178455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536599</v>
+        <v>122536600</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,12 +1293,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598450</v>
+        <v>598566</v>
       </c>
       <c r="R7" t="n">
-        <v>7178455</v>
+        <v>7178644</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536599</v>
+        <v>122536600</v>
       </c>
       <c r="B6" t="n">
         <v>56594</v>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598450</v>
+        <v>598566</v>
       </c>
       <c r="R6" t="n">
-        <v>7178455</v>
+        <v>7178644</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,7 +1263,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536600</v>
+        <v>122536599</v>
       </c>
       <c r="B7" t="n">
         <v>56594</v>
@@ -1293,12 +1298,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1312,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598566</v>
+        <v>598450</v>
       </c>
       <c r="R7" t="n">
-        <v>7178644</v>
+        <v>7178455</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,12 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536600</v>
+        <v>122536599</v>
       </c>
       <c r="B6" t="n">
         <v>56688</v>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598566</v>
+        <v>598450</v>
       </c>
       <c r="R6" t="n">
-        <v>7178644</v>
+        <v>7178455</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536599</v>
+        <v>122536600</v>
       </c>
       <c r="B7" t="n">
         <v>56688</v>
@@ -1298,12 +1293,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1317,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598450</v>
+        <v>598566</v>
       </c>
       <c r="R7" t="n">
-        <v>7178455</v>
+        <v>7178644</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 25036-2024 artfynd.xlsx
+++ b/artfynd/A 25036-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>121497160</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -790,12 +785,7 @@
         <v>121497159</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497156</v>
+        <v>122536599</v>
       </c>
       <c r="B4" t="n">
-        <v>97073</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,34 +909,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Annevare, Ås lm</t>
+          <t>Tjärnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598473</v>
+        <v>598450</v>
       </c>
       <c r="R4" t="n">
-        <v>7178492</v>
+        <v>7178455</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,22 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497157</v>
+        <v>122536600</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,34 +1030,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Annevare, Ås lm</t>
+          <t>Tjärnmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598471</v>
+        <v>598566</v>
       </c>
       <c r="R5" t="n">
-        <v>7178490</v>
+        <v>7178644</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,22 +1098,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,15 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536599</v>
+        <v>121497156</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,48 +1156,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjärnmyran, Ås lm</t>
+          <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598450</v>
+        <v>598473</v>
       </c>
       <c r="R6" t="n">
-        <v>7178455</v>
+        <v>7178492</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,22 +1210,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536600</v>
+        <v>121497157</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,48 +1263,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjärnmyran, Ås lm</t>
+          <t>Södra Annevare, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598566</v>
+        <v>598471</v>
       </c>
       <c r="R7" t="n">
-        <v>7178644</v>
+        <v>7178490</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,27 +1317,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I dessa ingår möjligen de längre söderut på Tjärnmyran som kan ha flyttat sig hit</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
